--- a/property listing details- 1-june-2026.xlsx
+++ b/property listing details- 1-june-2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\vikas mehta , mehta estates patel nagar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USET\Desktop\WORK\PROJECTS\Real-Estate-Project\realstate\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF83C3B-CC1A-481B-8D82-F87ED6D012DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="22410" windowHeight="12165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Property Listing Fields" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="152">
   <si>
     <t>Section</t>
   </si>
@@ -472,13 +473,16 @@
   </si>
   <si>
     <t xml:space="preserve">Keys Avilability </t>
+  </si>
+  <si>
+    <t>social medi amarketting tab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,15 +605,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -626,6 +621,15 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -927,17 +931,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C145"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C147"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="44.453125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="18.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -948,8 +952,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -959,8 +963,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+    <row r="3" spans="1:3" ht="90">
+      <c r="A3" s="12"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -968,8 +972,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
+    <row r="4" spans="1:3">
+      <c r="A4" s="12"/>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
@@ -977,8 +981,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13"/>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -986,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -997,8 +1001,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:3" ht="30">
+      <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1008,8 +1012,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
+    <row r="8" spans="1:3" ht="30">
+      <c r="A8" s="12"/>
       <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
@@ -1017,8 +1021,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:3">
+      <c r="A9" s="12"/>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
@@ -1026,8 +1030,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
+    <row r="10" spans="1:3" ht="30">
+      <c r="A10" s="12"/>
       <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1035,8 +1039,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
+    <row r="11" spans="1:3" ht="30">
+      <c r="A11" s="13"/>
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
@@ -1044,8 +1048,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1055,8 +1059,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
+    <row r="13" spans="1:3" ht="30">
+      <c r="A13" s="13"/>
       <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
@@ -1064,7 +1068,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="30">
       <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
@@ -1075,7 +1079,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="30">
       <c r="A15" s="4" t="s">
         <v>33</v>
       </c>
@@ -1086,7 +1090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="60">
       <c r="A16" s="4" t="s">
         <v>36</v>
       </c>
@@ -1097,7 +1101,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="30">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
@@ -1108,7 +1112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="30">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -1119,8 +1123,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:3" ht="60">
+      <c r="A19" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1130,8 +1134,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
+    <row r="20" spans="1:3" ht="45">
+      <c r="A20" s="12"/>
       <c r="B20" s="3" t="s">
         <v>45</v>
       </c>
@@ -1139,8 +1143,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
+    <row r="21" spans="1:3" ht="30">
+      <c r="A21" s="12"/>
       <c r="B21" s="3" t="s">
         <v>47</v>
       </c>
@@ -1148,8 +1152,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
+    <row r="22" spans="1:3" ht="30">
+      <c r="A22" s="12"/>
       <c r="B22" s="3" t="s">
         <v>49</v>
       </c>
@@ -1157,8 +1161,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
+    <row r="23" spans="1:3" ht="30">
+      <c r="A23" s="12"/>
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
@@ -1166,8 +1170,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12"/>
       <c r="B24" s="3" t="s">
         <v>53</v>
       </c>
@@ -1175,8 +1179,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
+    <row r="25" spans="1:3" ht="30">
+      <c r="A25" s="12"/>
       <c r="B25" s="3" t="s">
         <v>55</v>
       </c>
@@ -1184,8 +1188,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="6"/>
+    <row r="26" spans="1:3" ht="30">
+      <c r="A26" s="12"/>
       <c r="B26" s="3" t="s">
         <v>57</v>
       </c>
@@ -1193,8 +1197,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="6"/>
+    <row r="27" spans="1:3" ht="30">
+      <c r="A27" s="12"/>
       <c r="B27" s="3" t="s">
         <v>59</v>
       </c>
@@ -1202,8 +1206,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="6"/>
+    <row r="28" spans="1:3">
+      <c r="A28" s="12"/>
       <c r="B28" s="3" t="s">
         <v>61</v>
       </c>
@@ -1211,8 +1215,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="6"/>
+    <row r="29" spans="1:3">
+      <c r="A29" s="12"/>
       <c r="B29" s="3" t="s">
         <v>63</v>
       </c>
@@ -1220,8 +1224,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="6"/>
+    <row r="30" spans="1:3">
+      <c r="A30" s="12"/>
       <c r="B30" s="3" t="s">
         <v>64</v>
       </c>
@@ -1229,8 +1233,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="6"/>
+    <row r="31" spans="1:3">
+      <c r="A31" s="12"/>
       <c r="B31" s="3" t="s">
         <v>65</v>
       </c>
@@ -1238,8 +1242,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="6"/>
+    <row r="32" spans="1:3" ht="30">
+      <c r="A32" s="12"/>
       <c r="B32" s="3" t="s">
         <v>67</v>
       </c>
@@ -1247,8 +1251,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="6"/>
+    <row r="33" spans="1:3" ht="30">
+      <c r="A33" s="12"/>
       <c r="B33" s="3" t="s">
         <v>69</v>
       </c>
@@ -1256,8 +1260,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A34" s="6"/>
+    <row r="34" spans="1:3" ht="30">
+      <c r="A34" s="12"/>
       <c r="B34" s="3" t="s">
         <v>71</v>
       </c>
@@ -1265,8 +1269,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="6"/>
+    <row r="35" spans="1:3" ht="30">
+      <c r="A35" s="12"/>
       <c r="B35" s="3" t="s">
         <v>73</v>
       </c>
@@ -1274,8 +1278,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="6"/>
+    <row r="36" spans="1:3" ht="30">
+      <c r="A36" s="12"/>
       <c r="B36" s="3" t="s">
         <v>74</v>
       </c>
@@ -1283,8 +1287,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="6"/>
+    <row r="37" spans="1:3" ht="30">
+      <c r="A37" s="12"/>
       <c r="B37" s="3" t="s">
         <v>76</v>
       </c>
@@ -1292,8 +1296,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="6"/>
+    <row r="38" spans="1:3">
+      <c r="A38" s="12"/>
       <c r="B38" s="3" t="s">
         <v>77</v>
       </c>
@@ -1301,8 +1305,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="6"/>
+    <row r="39" spans="1:3">
+      <c r="A39" s="12"/>
       <c r="B39" s="3" t="s">
         <v>78</v>
       </c>
@@ -1310,8 +1314,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="6"/>
+    <row r="40" spans="1:3" ht="30">
+      <c r="A40" s="12"/>
       <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
@@ -1319,8 +1323,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="7"/>
+    <row r="41" spans="1:3">
+      <c r="A41" s="13"/>
       <c r="B41" s="3" t="s">
         <v>81</v>
       </c>
@@ -1328,8 +1332,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:3" ht="30">
+      <c r="A42" s="11" t="s">
         <v>82</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -1339,8 +1343,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="7"/>
+    <row r="43" spans="1:3">
+      <c r="A43" s="13"/>
       <c r="B43" s="3" t="s">
         <v>85</v>
       </c>
@@ -1348,8 +1352,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:3" ht="30">
+      <c r="A44" s="11" t="s">
         <v>87</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -1359,8 +1363,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="6"/>
+    <row r="45" spans="1:3" ht="30">
+      <c r="A45" s="12"/>
       <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
@@ -1368,8 +1372,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="6"/>
+    <row r="46" spans="1:3" ht="30">
+      <c r="A46" s="12"/>
       <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
@@ -1377,8 +1381,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="6"/>
+    <row r="47" spans="1:3">
+      <c r="A47" s="12"/>
       <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
@@ -1386,8 +1390,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A48" s="7"/>
+    <row r="48" spans="1:3" ht="30">
+      <c r="A48" s="13"/>
       <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
@@ -1395,7 +1399,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="60">
       <c r="A49" s="4" t="s">
         <v>98</v>
       </c>
@@ -1406,387 +1410,392 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="8">
+    <row r="52" spans="1:3">
+      <c r="A52" s="5">
         <v>31573</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="10"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="9"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="10" t="s">
+    <row r="56" spans="1:3">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="6"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="10" t="s">
+    <row r="59" spans="1:3">
+      <c r="A59" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="10" t="s">
+    <row r="60" spans="1:3">
+      <c r="A60" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="10" t="s">
+    <row r="61" spans="1:3">
+      <c r="A61" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="10" t="s">
+    <row r="62" spans="1:3">
+      <c r="A62" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="9"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="10" t="s">
+    <row r="63" spans="1:3">
+      <c r="A63" s="6"/>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="10" t="s">
+    <row r="65" spans="1:1">
+      <c r="A65" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="10" t="s">
+    <row r="66" spans="1:1">
+      <c r="A66" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="9"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="10" t="s">
+    <row r="67" spans="1:1">
+      <c r="A67" s="6"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="10" t="s">
+    <row r="69" spans="1:1">
+      <c r="A69" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="10" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="10" t="s">
+    <row r="71" spans="1:1">
+      <c r="A71" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="9"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="10" t="s">
+    <row r="72" spans="1:1">
+      <c r="A72" s="6"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" s="10" t="s">
+    <row r="74" spans="1:1">
+      <c r="A74" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" s="10" t="s">
+    <row r="75" spans="1:1">
+      <c r="A75" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" s="9"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" s="10" t="s">
+    <row r="76" spans="1:1">
+      <c r="A76" s="6"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" s="10" t="s">
+    <row r="78" spans="1:1">
+      <c r="A78" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" s="10" t="s">
+    <row r="79" spans="1:1">
+      <c r="A79" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" s="9"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="10" t="s">
+    <row r="80" spans="1:1">
+      <c r="A80" s="6"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" s="9"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" s="10" t="s">
+    <row r="82" spans="1:1">
+      <c r="A82" s="6"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="11" t="s">
+    <row r="85" spans="1:1" ht="18">
+      <c r="A85" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" s="12"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="12" t="s">
+    <row r="86" spans="1:1">
+      <c r="A86" s="9"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" s="12"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" s="12" t="s">
+    <row r="88" spans="1:1">
+      <c r="A88" s="9"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" s="12"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" s="12" t="s">
+    <row r="90" spans="1:1">
+      <c r="A90" s="9"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" s="12"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" s="12" t="s">
+    <row r="92" spans="1:1">
+      <c r="A92" s="9"/>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" s="12"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" s="12" t="s">
+    <row r="94" spans="1:1">
+      <c r="A94" s="9"/>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" s="12"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" s="12" t="s">
+    <row r="96" spans="1:1">
+      <c r="A96" s="9"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" s="12"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" s="12" t="s">
+    <row r="98" spans="1:1">
+      <c r="A98" s="9"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="11" t="s">
+    <row r="101" spans="1:1" ht="18">
+      <c r="A101" s="8" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" s="13" t="s">
+    <row r="103" spans="1:1">
+      <c r="A103" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A104" s="12"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A105" s="12" t="s">
+    <row r="104" spans="1:1">
+      <c r="A104" s="9"/>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A106" s="12"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" s="12" t="s">
+    <row r="106" spans="1:1">
+      <c r="A106" s="9"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A108" s="12"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" s="12" t="s">
+    <row r="108" spans="1:1">
+      <c r="A108" s="9"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A110" s="12"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A111" s="12" t="s">
+    <row r="110" spans="1:1">
+      <c r="A110" s="9"/>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A112" s="12"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A113" s="12" t="s">
+    <row r="112" spans="1:1">
+      <c r="A112" s="9"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A114" s="12"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A115" s="12" t="s">
+    <row r="114" spans="1:1">
+      <c r="A114" s="9"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A117" s="13" t="s">
+    <row r="117" spans="1:1">
+      <c r="A117" s="10" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" s="12"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A119" s="12" t="s">
+    <row r="118" spans="1:1">
+      <c r="A118" s="9"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" s="12"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A121" s="12" t="s">
+    <row r="120" spans="1:1">
+      <c r="A120" s="9"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A122" s="12"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A123" s="12" t="s">
+    <row r="122" spans="1:1">
+      <c r="A122" s="9"/>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A124" s="12"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A125" s="12" t="s">
+    <row r="124" spans="1:1">
+      <c r="A124" s="9"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A127" s="13" t="s">
+    <row r="127" spans="1:1">
+      <c r="A127" s="10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A128" s="12"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A129" s="12" t="s">
+    <row r="128" spans="1:1">
+      <c r="A128" s="9"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" s="12"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A131" s="12" t="s">
+    <row r="130" spans="1:1">
+      <c r="A130" s="9"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" s="12"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A133" s="12" t="s">
+    <row r="132" spans="1:1">
+      <c r="A132" s="9"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A134" s="12"/>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A135" s="12" t="s">
+    <row r="134" spans="1:1">
+      <c r="A134" s="9"/>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="9" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A137" s="13" t="s">
+    <row r="137" spans="1:1">
+      <c r="A137" s="10" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A138" s="12"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A139" s="12" t="s">
+    <row r="138" spans="1:1">
+      <c r="A138" s="9"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A140" s="12"/>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A141" s="12" t="s">
+    <row r="140" spans="1:1">
+      <c r="A140" s="9"/>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A142" s="12"/>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A143" s="12" t="s">
+    <row r="142" spans="1:1">
+      <c r="A142" s="9"/>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="9" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A145" s="13" t="s">
+    <row r="145" spans="1:1">
+      <c r="A145" s="10" t="s">
         <v>150</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="30">
+      <c r="A147" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
